--- a/artfynd/A 41917-2026 artfynd.xlsx
+++ b/artfynd/A 41917-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137232281</v>
       </c>
       <c r="B2" t="n">
-        <v>92143</v>
+        <v>92145</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>137232291</v>
       </c>
       <c r="B3" t="n">
-        <v>92575</v>
+        <v>92577</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -895,7 +895,7 @@
         <v>137232324</v>
       </c>
       <c r="B4" t="n">
-        <v>97499</v>
+        <v>97501</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1002,7 +1002,7 @@
         <v>137232777</v>
       </c>
       <c r="B5" t="n">
-        <v>92164</v>
+        <v>92166</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1121,7 +1121,7 @@
         <v>137232386</v>
       </c>
       <c r="B6" t="n">
-        <v>79501</v>
+        <v>79503</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1232,7 +1232,7 @@
         <v>137232556</v>
       </c>
       <c r="B7" t="n">
-        <v>79501</v>
+        <v>79503</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1343,7 +1343,7 @@
         <v>137232618</v>
       </c>
       <c r="B8" t="n">
-        <v>79501</v>
+        <v>79503</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1454,7 +1454,7 @@
         <v>137232276</v>
       </c>
       <c r="B9" t="n">
-        <v>58018</v>
+        <v>58020</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1569,7 +1569,7 @@
         <v>137232728</v>
       </c>
       <c r="B10" t="n">
-        <v>58018</v>
+        <v>58020</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1684,7 +1684,7 @@
         <v>137232447</v>
       </c>
       <c r="B11" t="n">
-        <v>58021</v>
+        <v>58023</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1799,7 +1799,7 @@
         <v>137232480</v>
       </c>
       <c r="B12" t="n">
-        <v>58021</v>
+        <v>58023</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1922,7 +1922,7 @@
         <v>137232407</v>
       </c>
       <c r="B13" t="n">
-        <v>58182</v>
+        <v>58184</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2036,7 +2036,7 @@
         <v>137232257</v>
       </c>
       <c r="B14" t="n">
-        <v>8463</v>
+        <v>8464</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2148,7 +2148,7 @@
         <v>137232312</v>
       </c>
       <c r="B15" t="n">
-        <v>8463</v>
+        <v>8464</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2260,7 +2260,7 @@
         <v>137232539</v>
       </c>
       <c r="B16" t="n">
-        <v>8463</v>
+        <v>8464</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2372,7 +2372,7 @@
         <v>137232571</v>
       </c>
       <c r="B17" t="n">
-        <v>8463</v>
+        <v>8464</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2484,7 +2484,7 @@
         <v>137232581</v>
       </c>
       <c r="B18" t="n">
-        <v>8463</v>
+        <v>8464</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2596,7 +2596,7 @@
         <v>137232595</v>
       </c>
       <c r="B19" t="n">
-        <v>8463</v>
+        <v>8464</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2708,7 +2708,7 @@
         <v>137232605</v>
       </c>
       <c r="B20" t="n">
-        <v>8463</v>
+        <v>8464</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2820,7 +2820,7 @@
         <v>137232818</v>
       </c>
       <c r="B21" t="n">
-        <v>98257</v>
+        <v>98259</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2927,7 +2927,7 @@
         <v>137232523</v>
       </c>
       <c r="B22" t="n">
-        <v>98251</v>
+        <v>98253</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3034,7 +3034,7 @@
         <v>137232790</v>
       </c>
       <c r="B23" t="n">
-        <v>98251</v>
+        <v>98253</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3141,7 +3141,7 @@
         <v>137232813</v>
       </c>
       <c r="B24" t="n">
-        <v>98254</v>
+        <v>98256</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>

--- a/artfynd/A 41917-2026 artfynd.xlsx
+++ b/artfynd/A 41917-2026 artfynd.xlsx
@@ -1482,11 +1482,7 @@
       <c r="I9" t="inlineStr"/>
       <c r="K9" t="inlineStr"/>
       <c r="L9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
+      <c r="M9" t="inlineStr"/>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
@@ -1597,11 +1593,7 @@
       <c r="I10" t="inlineStr"/>
       <c r="K10" t="inlineStr"/>
       <c r="L10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
+      <c r="M10" t="inlineStr"/>
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
@@ -1712,11 +1704,7 @@
       <c r="I11" t="inlineStr"/>
       <c r="K11" t="inlineStr"/>
       <c r="L11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
+      <c r="M11" t="inlineStr"/>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
@@ -1830,16 +1818,8 @@
         </is>
       </c>
       <c r="K12" t="inlineStr"/>
-      <c r="L12" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
+      <c r="L12" t="inlineStr"/>
+      <c r="M12" t="inlineStr"/>
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
@@ -1954,11 +1934,7 @@
       </c>
       <c r="K13" t="inlineStr"/>
       <c r="L13" t="inlineStr"/>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
+      <c r="M13" t="inlineStr"/>
       <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
@@ -2065,11 +2041,7 @@
       <c r="J14" t="inlineStr"/>
       <c r="K14" t="inlineStr"/>
       <c r="L14" t="inlineStr"/>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
+      <c r="M14" t="inlineStr"/>
       <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
@@ -2177,11 +2149,7 @@
       <c r="J15" t="inlineStr"/>
       <c r="K15" t="inlineStr"/>
       <c r="L15" t="inlineStr"/>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
+      <c r="M15" t="inlineStr"/>
       <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
@@ -2289,11 +2257,7 @@
       <c r="J16" t="inlineStr"/>
       <c r="K16" t="inlineStr"/>
       <c r="L16" t="inlineStr"/>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
+      <c r="M16" t="inlineStr"/>
       <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
@@ -2401,11 +2365,7 @@
       <c r="J17" t="inlineStr"/>
       <c r="K17" t="inlineStr"/>
       <c r="L17" t="inlineStr"/>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
+      <c r="M17" t="inlineStr"/>
       <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
@@ -2513,11 +2473,7 @@
       <c r="J18" t="inlineStr"/>
       <c r="K18" t="inlineStr"/>
       <c r="L18" t="inlineStr"/>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
+      <c r="M18" t="inlineStr"/>
       <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
@@ -2625,11 +2581,7 @@
       <c r="J19" t="inlineStr"/>
       <c r="K19" t="inlineStr"/>
       <c r="L19" t="inlineStr"/>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
+      <c r="M19" t="inlineStr"/>
       <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
@@ -2737,11 +2689,7 @@
       <c r="J20" t="inlineStr"/>
       <c r="K20" t="inlineStr"/>
       <c r="L20" t="inlineStr"/>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
+      <c r="M20" t="inlineStr"/>
       <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>

--- a/artfynd/A 41917-2026 artfynd.xlsx
+++ b/artfynd/A 41917-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137232281</v>
       </c>
       <c r="B2" t="n">
-        <v>92145</v>
+        <v>92148</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>137232291</v>
       </c>
       <c r="B3" t="n">
-        <v>92577</v>
+        <v>92580</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -895,7 +895,7 @@
         <v>137232324</v>
       </c>
       <c r="B4" t="n">
-        <v>97501</v>
+        <v>97504</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1002,7 +1002,7 @@
         <v>137232777</v>
       </c>
       <c r="B5" t="n">
-        <v>92166</v>
+        <v>92169</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -2768,7 +2768,7 @@
         <v>137232818</v>
       </c>
       <c r="B21" t="n">
-        <v>98259</v>
+        <v>98262</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2875,7 +2875,7 @@
         <v>137232523</v>
       </c>
       <c r="B22" t="n">
-        <v>98253</v>
+        <v>98256</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2982,7 +2982,7 @@
         <v>137232790</v>
       </c>
       <c r="B23" t="n">
-        <v>98253</v>
+        <v>98256</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3089,7 +3089,7 @@
         <v>137232813</v>
       </c>
       <c r="B24" t="n">
-        <v>98256</v>
+        <v>98259</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>

--- a/artfynd/A 41917-2026 artfynd.xlsx
+++ b/artfynd/A 41917-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137232281</v>
       </c>
       <c r="B2" t="n">
-        <v>92148</v>
+        <v>92158</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>137232291</v>
       </c>
       <c r="B3" t="n">
-        <v>92580</v>
+        <v>92590</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -895,7 +895,7 @@
         <v>137232324</v>
       </c>
       <c r="B4" t="n">
-        <v>97504</v>
+        <v>97514</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1002,7 +1002,7 @@
         <v>137232777</v>
       </c>
       <c r="B5" t="n">
-        <v>92169</v>
+        <v>92179</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1121,7 +1121,7 @@
         <v>137232386</v>
       </c>
       <c r="B6" t="n">
-        <v>79503</v>
+        <v>79513</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1232,7 +1232,7 @@
         <v>137232556</v>
       </c>
       <c r="B7" t="n">
-        <v>79503</v>
+        <v>79513</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1343,7 +1343,7 @@
         <v>137232618</v>
       </c>
       <c r="B8" t="n">
-        <v>79503</v>
+        <v>79513</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1454,7 +1454,7 @@
         <v>137232276</v>
       </c>
       <c r="B9" t="n">
-        <v>58020</v>
+        <v>58030</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1565,7 +1565,7 @@
         <v>137232728</v>
       </c>
       <c r="B10" t="n">
-        <v>58020</v>
+        <v>58030</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1676,7 +1676,7 @@
         <v>137232447</v>
       </c>
       <c r="B11" t="n">
-        <v>58023</v>
+        <v>58033</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1787,7 +1787,7 @@
         <v>137232480</v>
       </c>
       <c r="B12" t="n">
-        <v>58023</v>
+        <v>58033</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1902,7 +1902,7 @@
         <v>137232407</v>
       </c>
       <c r="B13" t="n">
-        <v>58184</v>
+        <v>58194</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2012,7 +2012,7 @@
         <v>137232257</v>
       </c>
       <c r="B14" t="n">
-        <v>8464</v>
+        <v>8470</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2120,7 +2120,7 @@
         <v>137232312</v>
       </c>
       <c r="B15" t="n">
-        <v>8464</v>
+        <v>8470</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2228,7 +2228,7 @@
         <v>137232539</v>
       </c>
       <c r="B16" t="n">
-        <v>8464</v>
+        <v>8470</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2336,7 +2336,7 @@
         <v>137232571</v>
       </c>
       <c r="B17" t="n">
-        <v>8464</v>
+        <v>8470</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2444,7 +2444,7 @@
         <v>137232581</v>
       </c>
       <c r="B18" t="n">
-        <v>8464</v>
+        <v>8470</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2552,7 +2552,7 @@
         <v>137232595</v>
       </c>
       <c r="B19" t="n">
-        <v>8464</v>
+        <v>8470</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2660,7 +2660,7 @@
         <v>137232605</v>
       </c>
       <c r="B20" t="n">
-        <v>8464</v>
+        <v>8470</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2768,7 +2768,7 @@
         <v>137232818</v>
       </c>
       <c r="B21" t="n">
-        <v>98262</v>
+        <v>98272</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2875,7 +2875,7 @@
         <v>137232523</v>
       </c>
       <c r="B22" t="n">
-        <v>98256</v>
+        <v>98266</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2982,7 +2982,7 @@
         <v>137232790</v>
       </c>
       <c r="B23" t="n">
-        <v>98256</v>
+        <v>98266</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3089,7 +3089,7 @@
         <v>137232813</v>
       </c>
       <c r="B24" t="n">
-        <v>98259</v>
+        <v>98269</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>

--- a/artfynd/A 41917-2026 artfynd.xlsx
+++ b/artfynd/A 41917-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137232281</v>
       </c>
       <c r="B2" t="n">
-        <v>92158</v>
+        <v>92159</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>137232291</v>
       </c>
       <c r="B3" t="n">
-        <v>92590</v>
+        <v>92591</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -895,7 +895,7 @@
         <v>137232324</v>
       </c>
       <c r="B4" t="n">
-        <v>97514</v>
+        <v>97515</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1002,7 +1002,7 @@
         <v>137232777</v>
       </c>
       <c r="B5" t="n">
-        <v>92179</v>
+        <v>92180</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -2768,7 +2768,7 @@
         <v>137232818</v>
       </c>
       <c r="B21" t="n">
-        <v>98272</v>
+        <v>98273</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2875,7 +2875,7 @@
         <v>137232523</v>
       </c>
       <c r="B22" t="n">
-        <v>98266</v>
+        <v>98267</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2982,7 +2982,7 @@
         <v>137232790</v>
       </c>
       <c r="B23" t="n">
-        <v>98266</v>
+        <v>98267</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3089,7 +3089,7 @@
         <v>137232813</v>
       </c>
       <c r="B24" t="n">
-        <v>98269</v>
+        <v>98270</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>

--- a/artfynd/A 41917-2026 artfynd.xlsx
+++ b/artfynd/A 41917-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137232281</v>
       </c>
       <c r="B2" t="n">
-        <v>92159</v>
+        <v>92162</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>137232291</v>
       </c>
       <c r="B3" t="n">
-        <v>92591</v>
+        <v>92594</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -895,7 +895,7 @@
         <v>137232324</v>
       </c>
       <c r="B4" t="n">
-        <v>97515</v>
+        <v>97520</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1002,7 +1002,7 @@
         <v>137232777</v>
       </c>
       <c r="B5" t="n">
-        <v>92180</v>
+        <v>92183</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1121,7 +1121,7 @@
         <v>137232386</v>
       </c>
       <c r="B6" t="n">
-        <v>79513</v>
+        <v>79516</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1232,7 +1232,7 @@
         <v>137232556</v>
       </c>
       <c r="B7" t="n">
-        <v>79513</v>
+        <v>79516</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1343,7 +1343,7 @@
         <v>137232618</v>
       </c>
       <c r="B8" t="n">
-        <v>79513</v>
+        <v>79516</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1454,7 +1454,7 @@
         <v>137232276</v>
       </c>
       <c r="B9" t="n">
-        <v>58030</v>
+        <v>58031</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1565,7 +1565,7 @@
         <v>137232728</v>
       </c>
       <c r="B10" t="n">
-        <v>58030</v>
+        <v>58031</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1676,7 +1676,7 @@
         <v>137232447</v>
       </c>
       <c r="B11" t="n">
-        <v>58033</v>
+        <v>58034</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1787,7 +1787,7 @@
         <v>137232480</v>
       </c>
       <c r="B12" t="n">
-        <v>58033</v>
+        <v>58034</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1902,7 +1902,7 @@
         <v>137232407</v>
       </c>
       <c r="B13" t="n">
-        <v>58194</v>
+        <v>58195</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2768,7 +2768,7 @@
         <v>137232818</v>
       </c>
       <c r="B21" t="n">
-        <v>98273</v>
+        <v>98278</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2875,7 +2875,7 @@
         <v>137232523</v>
       </c>
       <c r="B22" t="n">
-        <v>98267</v>
+        <v>98272</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2982,7 +2982,7 @@
         <v>137232790</v>
       </c>
       <c r="B23" t="n">
-        <v>98267</v>
+        <v>98272</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3089,7 +3089,7 @@
         <v>137232813</v>
       </c>
       <c r="B24" t="n">
-        <v>98270</v>
+        <v>98275</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>

--- a/artfynd/A 41917-2026 artfynd.xlsx
+++ b/artfynd/A 41917-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137232281</v>
       </c>
       <c r="B2" t="n">
-        <v>92162</v>
+        <v>92164</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>137232291</v>
       </c>
       <c r="B3" t="n">
-        <v>92594</v>
+        <v>92596</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -895,7 +895,7 @@
         <v>137232324</v>
       </c>
       <c r="B4" t="n">
-        <v>97520</v>
+        <v>97522</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1002,7 +1002,7 @@
         <v>137232777</v>
       </c>
       <c r="B5" t="n">
-        <v>92183</v>
+        <v>92185</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -2768,7 +2768,7 @@
         <v>137232818</v>
       </c>
       <c r="B21" t="n">
-        <v>98278</v>
+        <v>98280</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2875,7 +2875,7 @@
         <v>137232523</v>
       </c>
       <c r="B22" t="n">
-        <v>98272</v>
+        <v>98274</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2982,7 +2982,7 @@
         <v>137232790</v>
       </c>
       <c r="B23" t="n">
-        <v>98272</v>
+        <v>98274</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3089,7 +3089,7 @@
         <v>137232813</v>
       </c>
       <c r="B24" t="n">
-        <v>98275</v>
+        <v>98277</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>

--- a/artfynd/A 41917-2026 artfynd.xlsx
+++ b/artfynd/A 41917-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137232281</v>
       </c>
       <c r="B2" t="n">
-        <v>92164</v>
+        <v>92169</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>137232291</v>
       </c>
       <c r="B3" t="n">
-        <v>92596</v>
+        <v>92601</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -895,7 +895,7 @@
         <v>137232324</v>
       </c>
       <c r="B4" t="n">
-        <v>97522</v>
+        <v>97528</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1002,7 +1002,7 @@
         <v>137232777</v>
       </c>
       <c r="B5" t="n">
-        <v>92185</v>
+        <v>92190</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1121,7 +1121,7 @@
         <v>137232386</v>
       </c>
       <c r="B6" t="n">
-        <v>79516</v>
+        <v>79521</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1232,7 +1232,7 @@
         <v>137232556</v>
       </c>
       <c r="B7" t="n">
-        <v>79516</v>
+        <v>79521</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1343,7 +1343,7 @@
         <v>137232618</v>
       </c>
       <c r="B8" t="n">
-        <v>79516</v>
+        <v>79521</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1454,7 +1454,7 @@
         <v>137232276</v>
       </c>
       <c r="B9" t="n">
-        <v>58031</v>
+        <v>58032</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1565,7 +1565,7 @@
         <v>137232728</v>
       </c>
       <c r="B10" t="n">
-        <v>58031</v>
+        <v>58032</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1676,7 +1676,7 @@
         <v>137232447</v>
       </c>
       <c r="B11" t="n">
-        <v>58034</v>
+        <v>58035</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1787,7 +1787,7 @@
         <v>137232480</v>
       </c>
       <c r="B12" t="n">
-        <v>58034</v>
+        <v>58035</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1902,7 +1902,7 @@
         <v>137232407</v>
       </c>
       <c r="B13" t="n">
-        <v>58195</v>
+        <v>58196</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2768,7 +2768,7 @@
         <v>137232818</v>
       </c>
       <c r="B21" t="n">
-        <v>98280</v>
+        <v>98286</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2875,7 +2875,7 @@
         <v>137232523</v>
       </c>
       <c r="B22" t="n">
-        <v>98274</v>
+        <v>98280</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2982,7 +2982,7 @@
         <v>137232790</v>
       </c>
       <c r="B23" t="n">
-        <v>98274</v>
+        <v>98280</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3089,7 +3089,7 @@
         <v>137232813</v>
       </c>
       <c r="B24" t="n">
-        <v>98277</v>
+        <v>98283</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>

--- a/artfynd/A 41917-2026 artfynd.xlsx
+++ b/artfynd/A 41917-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137232281</v>
       </c>
       <c r="B2" t="n">
-        <v>92169</v>
+        <v>92181</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>137232291</v>
       </c>
       <c r="B3" t="n">
-        <v>92601</v>
+        <v>92613</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -895,7 +895,7 @@
         <v>137232324</v>
       </c>
       <c r="B4" t="n">
-        <v>97528</v>
+        <v>97540</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1002,7 +1002,7 @@
         <v>137232777</v>
       </c>
       <c r="B5" t="n">
-        <v>92190</v>
+        <v>92202</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1121,7 +1121,7 @@
         <v>137232386</v>
       </c>
       <c r="B6" t="n">
-        <v>79521</v>
+        <v>79532</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1232,7 +1232,7 @@
         <v>137232556</v>
       </c>
       <c r="B7" t="n">
-        <v>79521</v>
+        <v>79532</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1343,7 +1343,7 @@
         <v>137232618</v>
       </c>
       <c r="B8" t="n">
-        <v>79521</v>
+        <v>79532</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -2768,7 +2768,7 @@
         <v>137232818</v>
       </c>
       <c r="B21" t="n">
-        <v>98286</v>
+        <v>98298</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2875,7 +2875,7 @@
         <v>137232523</v>
       </c>
       <c r="B22" t="n">
-        <v>98280</v>
+        <v>98292</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2982,7 +2982,7 @@
         <v>137232790</v>
       </c>
       <c r="B23" t="n">
-        <v>98280</v>
+        <v>98292</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3089,7 +3089,7 @@
         <v>137232813</v>
       </c>
       <c r="B24" t="n">
-        <v>98283</v>
+        <v>98295</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>

--- a/artfynd/A 41917-2026 artfynd.xlsx
+++ b/artfynd/A 41917-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137232281</v>
       </c>
       <c r="B2" t="n">
-        <v>92181</v>
+        <v>92182</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>137232291</v>
       </c>
       <c r="B3" t="n">
-        <v>92613</v>
+        <v>92614</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -895,7 +895,7 @@
         <v>137232324</v>
       </c>
       <c r="B4" t="n">
-        <v>97540</v>
+        <v>97541</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1002,7 +1002,7 @@
         <v>137232777</v>
       </c>
       <c r="B5" t="n">
-        <v>92202</v>
+        <v>92203</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1121,7 +1121,7 @@
         <v>137232386</v>
       </c>
       <c r="B6" t="n">
-        <v>79532</v>
+        <v>79533</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1232,7 +1232,7 @@
         <v>137232556</v>
       </c>
       <c r="B7" t="n">
-        <v>79532</v>
+        <v>79533</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1343,7 +1343,7 @@
         <v>137232618</v>
       </c>
       <c r="B8" t="n">
-        <v>79532</v>
+        <v>79533</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -2768,7 +2768,7 @@
         <v>137232818</v>
       </c>
       <c r="B21" t="n">
-        <v>98298</v>
+        <v>98299</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2875,7 +2875,7 @@
         <v>137232523</v>
       </c>
       <c r="B22" t="n">
-        <v>98292</v>
+        <v>98293</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2982,7 +2982,7 @@
         <v>137232790</v>
       </c>
       <c r="B23" t="n">
-        <v>98292</v>
+        <v>98293</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3089,7 +3089,7 @@
         <v>137232813</v>
       </c>
       <c r="B24" t="n">
-        <v>98295</v>
+        <v>98296</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>

--- a/artfynd/A 41917-2026 artfynd.xlsx
+++ b/artfynd/A 41917-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137232281</v>
       </c>
       <c r="B2" t="n">
-        <v>92182</v>
+        <v>92185</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>137232291</v>
       </c>
       <c r="B3" t="n">
-        <v>92614</v>
+        <v>92617</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -895,7 +895,7 @@
         <v>137232324</v>
       </c>
       <c r="B4" t="n">
-        <v>97541</v>
+        <v>97544</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1002,7 +1002,7 @@
         <v>137232777</v>
       </c>
       <c r="B5" t="n">
-        <v>92203</v>
+        <v>92206</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1121,7 +1121,7 @@
         <v>137232386</v>
       </c>
       <c r="B6" t="n">
-        <v>79533</v>
+        <v>79535</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1232,7 +1232,7 @@
         <v>137232556</v>
       </c>
       <c r="B7" t="n">
-        <v>79533</v>
+        <v>79535</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1343,7 +1343,7 @@
         <v>137232618</v>
       </c>
       <c r="B8" t="n">
-        <v>79533</v>
+        <v>79535</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -2768,7 +2768,7 @@
         <v>137232818</v>
       </c>
       <c r="B21" t="n">
-        <v>98299</v>
+        <v>98302</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2875,7 +2875,7 @@
         <v>137232523</v>
       </c>
       <c r="B22" t="n">
-        <v>98293</v>
+        <v>98296</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2982,7 +2982,7 @@
         <v>137232790</v>
       </c>
       <c r="B23" t="n">
-        <v>98293</v>
+        <v>98296</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3089,7 +3089,7 @@
         <v>137232813</v>
       </c>
       <c r="B24" t="n">
-        <v>98296</v>
+        <v>98299</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>

--- a/artfynd/A 41917-2026 artfynd.xlsx
+++ b/artfynd/A 41917-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137232281</v>
       </c>
       <c r="B2" t="n">
-        <v>92185</v>
+        <v>92189</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>137232291</v>
       </c>
       <c r="B3" t="n">
-        <v>92617</v>
+        <v>92621</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -895,7 +895,7 @@
         <v>137232324</v>
       </c>
       <c r="B4" t="n">
-        <v>97544</v>
+        <v>97548</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1002,7 +1002,7 @@
         <v>137232777</v>
       </c>
       <c r="B5" t="n">
-        <v>92206</v>
+        <v>92210</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1121,7 +1121,7 @@
         <v>137232386</v>
       </c>
       <c r="B6" t="n">
-        <v>79535</v>
+        <v>79539</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1232,7 +1232,7 @@
         <v>137232556</v>
       </c>
       <c r="B7" t="n">
-        <v>79535</v>
+        <v>79539</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1343,7 +1343,7 @@
         <v>137232618</v>
       </c>
       <c r="B8" t="n">
-        <v>79535</v>
+        <v>79539</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1454,7 +1454,7 @@
         <v>137232276</v>
       </c>
       <c r="B9" t="n">
-        <v>58032</v>
+        <v>58035</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1565,7 +1565,7 @@
         <v>137232728</v>
       </c>
       <c r="B10" t="n">
-        <v>58032</v>
+        <v>58035</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1676,7 +1676,7 @@
         <v>137232447</v>
       </c>
       <c r="B11" t="n">
-        <v>58035</v>
+        <v>58038</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1787,7 +1787,7 @@
         <v>137232480</v>
       </c>
       <c r="B12" t="n">
-        <v>58035</v>
+        <v>58038</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1902,7 +1902,7 @@
         <v>137232407</v>
       </c>
       <c r="B13" t="n">
-        <v>58196</v>
+        <v>58199</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2768,7 +2768,7 @@
         <v>137232818</v>
       </c>
       <c r="B21" t="n">
-        <v>98302</v>
+        <v>98306</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2875,7 +2875,7 @@
         <v>137232523</v>
       </c>
       <c r="B22" t="n">
-        <v>98296</v>
+        <v>98300</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2982,7 +2982,7 @@
         <v>137232790</v>
       </c>
       <c r="B23" t="n">
-        <v>98296</v>
+        <v>98300</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3089,7 +3089,7 @@
         <v>137232813</v>
       </c>
       <c r="B24" t="n">
-        <v>98299</v>
+        <v>98303</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
